--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="678" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C86F0B00-3CE0-425D-9074-453FAB671804}"/>
+  <xr:revisionPtr revIDLastSave="690" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F98A125-9A2A-4596-AEA3-EC75C35B0469}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue_Daily" sheetId="1" r:id="rId1"/>
@@ -3493,6 +3493,12 @@
       <c r="C172" t="s">
         <v>18</v>
       </c>
+      <c r="D172">
+        <v>3717</v>
+      </c>
+      <c r="E172">
+        <v>42</v>
+      </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
@@ -3504,6 +3510,12 @@
       <c r="C173" t="s">
         <v>18</v>
       </c>
+      <c r="D173">
+        <v>2674</v>
+      </c>
+      <c r="E173">
+        <v>31</v>
+      </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
@@ -8187,6 +8199,12 @@
       <c r="C506" t="s">
         <v>19</v>
       </c>
+      <c r="D506">
+        <v>12975</v>
+      </c>
+      <c r="E506">
+        <v>150</v>
+      </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
@@ -8198,6 +8216,12 @@
       <c r="C507" t="s">
         <v>19</v>
       </c>
+      <c r="D507">
+        <v>9995</v>
+      </c>
+      <c r="E507">
+        <v>107</v>
+      </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
@@ -12015,10 +12039,10 @@
         <v>18</v>
       </c>
       <c r="D789">
-        <v>4721.99</v>
+        <v>1983.85</v>
       </c>
       <c r="E789">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="790" spans="1:5" x14ac:dyDescent="0.35">
@@ -12116,6 +12140,12 @@
       <c r="C795" t="s">
         <v>18</v>
       </c>
+      <c r="D795">
+        <v>733.33333600000003</v>
+      </c>
+      <c r="E795">
+        <v>25</v>
+      </c>
     </row>
     <row r="796" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A796" s="1">
@@ -12127,6 +12157,12 @@
       <c r="C796" t="s">
         <v>18</v>
       </c>
+      <c r="D796">
+        <v>1193.3333359999999</v>
+      </c>
+      <c r="E796">
+        <v>20</v>
+      </c>
     </row>
     <row r="797" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A797" s="1">
@@ -15944,10 +15980,10 @@
         <v>19</v>
       </c>
       <c r="D1078">
-        <v>254.166664</v>
+        <v>4806.75</v>
       </c>
       <c r="E1078">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1079" spans="1:5" x14ac:dyDescent="0.35">
@@ -16045,6 +16081,12 @@
       <c r="C1084" t="s">
         <v>19</v>
       </c>
+      <c r="D1084">
+        <v>3790.258331</v>
+      </c>
+      <c r="E1084">
+        <v>37</v>
+      </c>
     </row>
     <row r="1085" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1085" s="1">
@@ -16055,6 +16097,12 @@
       </c>
       <c r="C1085" t="s">
         <v>19</v>
+      </c>
+      <c r="D1085">
+        <v>1014.166664</v>
+      </c>
+      <c r="E1085">
+        <v>30</v>
       </c>
     </row>
     <row r="1086" spans="1:5" x14ac:dyDescent="0.35">

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="690" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F98A125-9A2A-4596-AEA3-EC75C35B0469}"/>
+  <xr:revisionPtr revIDLastSave="698" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E62D065E-3E23-4E5A-9F5B-7501D77E76D0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -3527,6 +3527,12 @@
       <c r="C174" t="s">
         <v>18</v>
       </c>
+      <c r="D174">
+        <v>4371</v>
+      </c>
+      <c r="E174">
+        <v>59</v>
+      </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
@@ -8233,6 +8239,12 @@
       <c r="C508" t="s">
         <v>19</v>
       </c>
+      <c r="D508">
+        <v>17514</v>
+      </c>
+      <c r="E508">
+        <v>192</v>
+      </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
@@ -12174,6 +12186,12 @@
       <c r="C797" t="s">
         <v>18</v>
       </c>
+      <c r="D797">
+        <v>1439.641672</v>
+      </c>
+      <c r="E797">
+        <v>21</v>
+      </c>
     </row>
     <row r="798" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A798" s="1">
@@ -16114,6 +16132,12 @@
       </c>
       <c r="C1086" t="s">
         <v>19</v>
+      </c>
+      <c r="D1086">
+        <v>2238.2499979999998</v>
+      </c>
+      <c r="E1086">
+        <v>31</v>
       </c>
     </row>
     <row r="1087" spans="1:5" x14ac:dyDescent="0.35">
@@ -40883,6 +40907,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -41105,27 +41149,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41144,25 +41187,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="698" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E62D065E-3E23-4E5A-9F5B-7501D77E76D0}"/>
+  <xr:revisionPtr revIDLastSave="707" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A55572A7-3CC2-4D9D-9299-7E74591C8C34}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -3544,6 +3544,12 @@
       <c r="C175" t="s">
         <v>18</v>
       </c>
+      <c r="D175">
+        <v>1892</v>
+      </c>
+      <c r="E175">
+        <v>28</v>
+      </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
@@ -3555,8 +3561,14 @@
       <c r="C176" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D176">
+        <v>3232</v>
+      </c>
+      <c r="E176">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>46229</v>
       </c>
@@ -3566,8 +3578,14 @@
       <c r="C177" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D177">
+        <v>4523</v>
+      </c>
+      <c r="E177">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>46230</v>
       </c>
@@ -3578,7 +3596,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>46231</v>
       </c>
@@ -3589,7 +3607,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>46232</v>
       </c>
@@ -3600,7 +3618,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>46233</v>
       </c>
@@ -3611,7 +3629,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>46234</v>
       </c>
@@ -3622,7 +3640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>46235</v>
       </c>
@@ -3633,7 +3651,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>46236</v>
       </c>
@@ -3644,7 +3662,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>46237</v>
       </c>
@@ -3655,7 +3673,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>46238</v>
       </c>
@@ -3666,7 +3684,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>46239</v>
       </c>
@@ -3677,7 +3695,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>46240</v>
       </c>
@@ -3688,7 +3706,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>46241</v>
       </c>
@@ -3699,7 +3717,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>46242</v>
       </c>
@@ -3710,7 +3728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>46243</v>
       </c>
@@ -3721,7 +3739,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>46244</v>
       </c>
@@ -8256,6 +8274,12 @@
       <c r="C509" t="s">
         <v>19</v>
       </c>
+      <c r="D509">
+        <v>17219</v>
+      </c>
+      <c r="E509">
+        <v>193</v>
+      </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
@@ -8267,6 +8291,12 @@
       <c r="C510" t="s">
         <v>19</v>
       </c>
+      <c r="D510">
+        <v>16310</v>
+      </c>
+      <c r="E510">
+        <v>190</v>
+      </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
@@ -8278,6 +8308,12 @@
       <c r="C511" t="s">
         <v>19</v>
       </c>
+      <c r="D511">
+        <v>12675</v>
+      </c>
+      <c r="E511">
+        <v>149</v>
+      </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
@@ -12203,6 +12239,12 @@
       <c r="C798" t="s">
         <v>18</v>
       </c>
+      <c r="D798">
+        <v>469.16666900000001</v>
+      </c>
+      <c r="E798">
+        <v>13</v>
+      </c>
     </row>
     <row r="799" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A799" s="1">
@@ -12214,6 +12256,12 @@
       <c r="C799" t="s">
         <v>18</v>
       </c>
+      <c r="D799">
+        <v>470.00000199999999</v>
+      </c>
+      <c r="E799">
+        <v>8</v>
+      </c>
     </row>
     <row r="800" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A800" s="1">
@@ -12225,6 +12273,12 @@
       <c r="C800" t="s">
         <v>18</v>
       </c>
+      <c r="D800">
+        <v>0</v>
+      </c>
+      <c r="E800">
+        <v>0</v>
+      </c>
     </row>
     <row r="801" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A801" s="1">
@@ -16150,6 +16204,12 @@
       <c r="C1087" t="s">
         <v>19</v>
       </c>
+      <c r="D1087">
+        <v>2566.4749870000001</v>
+      </c>
+      <c r="E1087">
+        <v>35</v>
+      </c>
     </row>
     <row r="1088" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1088" s="1">
@@ -16161,8 +16221,14 @@
       <c r="C1088" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1089" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1088">
+        <v>2857.5116560000001</v>
+      </c>
+      <c r="E1088">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1089" s="1">
         <v>46229</v>
       </c>
@@ -16172,8 +16238,14 @@
       <c r="C1089" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1090" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1089">
+        <v>0</v>
+      </c>
+      <c r="E1089">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1090" s="1">
         <v>46230</v>
       </c>
@@ -16184,7 +16256,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1091" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1091" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1091" s="1">
         <v>46231</v>
       </c>
@@ -16195,7 +16267,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1092" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1092" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1092" s="1">
         <v>46232</v>
       </c>
@@ -16206,7 +16278,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1093" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1093" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1093" s="1">
         <v>46233</v>
       </c>
@@ -16217,7 +16289,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1094" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1094" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1094" s="1">
         <v>46234</v>
       </c>
@@ -16228,7 +16300,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1095" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1095" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1095" s="1">
         <v>46235</v>
       </c>
@@ -16239,7 +16311,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1096" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1096" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1096" s="1">
         <v>46236</v>
       </c>
@@ -16250,7 +16322,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1097" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1097" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1097" s="1">
         <v>46237</v>
       </c>
@@ -16261,7 +16333,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1098" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1098" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1098" s="1">
         <v>46238</v>
       </c>
@@ -16272,7 +16344,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1099" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1099" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1099" s="1">
         <v>46239</v>
       </c>
@@ -16283,7 +16355,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1100" s="1">
         <v>46240</v>
       </c>
@@ -16294,7 +16366,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1101" s="1">
         <v>46241</v>
       </c>
@@ -16305,7 +16377,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1102" s="1">
         <v>46242</v>
       </c>
@@ -16316,7 +16388,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1103" s="1">
         <v>46243</v>
       </c>
@@ -16327,7 +16399,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1104" s="1">
         <v>46244</v>
       </c>
@@ -40907,26 +40979,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -41149,26 +41201,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41187,6 +41240,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="707" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A55572A7-3CC2-4D9D-9299-7E74591C8C34}"/>
+  <xr:revisionPtr revIDLastSave="715" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13CF1752-57E6-4869-905C-10D7172555AA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -3595,6 +3595,12 @@
       <c r="C178" t="s">
         <v>18</v>
       </c>
+      <c r="D178">
+        <v>3338</v>
+      </c>
+      <c r="E178">
+        <v>39</v>
+      </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
@@ -3606,6 +3612,12 @@
       <c r="C179" t="s">
         <v>18</v>
       </c>
+      <c r="D179">
+        <v>2817</v>
+      </c>
+      <c r="E179">
+        <v>47</v>
+      </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
@@ -3617,6 +3629,12 @@
       <c r="C180" t="s">
         <v>18</v>
       </c>
+      <c r="D180">
+        <v>1271</v>
+      </c>
+      <c r="E180">
+        <v>24</v>
+      </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
@@ -8325,8 +8343,14 @@
       <c r="C512" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D512">
+        <v>15386</v>
+      </c>
+      <c r="E512">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
         <v>46231</v>
       </c>
@@ -8336,8 +8360,14 @@
       <c r="C513" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D513">
+        <v>13294</v>
+      </c>
+      <c r="E513">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
         <v>46232</v>
       </c>
@@ -8347,8 +8377,14 @@
       <c r="C514" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D514">
+        <v>13577</v>
+      </c>
+      <c r="E514">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
         <v>46233</v>
       </c>
@@ -8359,7 +8395,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
         <v>46234</v>
       </c>
@@ -8370,7 +8406,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
         <v>46235</v>
       </c>
@@ -8381,7 +8417,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
         <v>46236</v>
       </c>
@@ -8392,7 +8428,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
         <v>46237</v>
       </c>
@@ -8403,7 +8439,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
         <v>46238</v>
       </c>
@@ -8414,7 +8450,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
         <v>46239</v>
       </c>
@@ -8425,7 +8461,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
         <v>46240</v>
       </c>
@@ -8436,7 +8472,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
         <v>46241</v>
       </c>
@@ -8447,7 +8483,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
         <v>46242</v>
       </c>
@@ -8458,7 +8494,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
         <v>46243</v>
       </c>
@@ -8469,7 +8505,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A526" s="1">
         <v>46244</v>
       </c>
@@ -8480,7 +8516,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
         <v>46245</v>
       </c>
@@ -8491,7 +8527,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
         <v>46246</v>
       </c>
@@ -12280,7 +12316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="801" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A801" s="1">
         <v>46230</v>
       </c>
@@ -12290,8 +12326,14 @@
       <c r="C801" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="802" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D801">
+        <v>45.833333000000003</v>
+      </c>
+      <c r="E801">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="802" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A802" s="1">
         <v>46231</v>
       </c>
@@ -12301,8 +12343,14 @@
       <c r="C802" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="803" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D802">
+        <v>272.50000199999999</v>
+      </c>
+      <c r="E802">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="803" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A803" s="1">
         <v>46232</v>
       </c>
@@ -12312,8 +12360,14 @@
       <c r="C803" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="804" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D803">
+        <v>676.22500300000002</v>
+      </c>
+      <c r="E803">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="804" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A804" s="1">
         <v>46233</v>
       </c>
@@ -12324,7 +12378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="805" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A805" s="1">
         <v>46234</v>
       </c>
@@ -12335,7 +12389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="806" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A806" s="1">
         <v>46235</v>
       </c>
@@ -12346,7 +12400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="807" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A807" s="1">
         <v>46236</v>
       </c>
@@ -12357,7 +12411,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="808" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A808" s="1">
         <v>46237</v>
       </c>
@@ -12368,7 +12422,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="809" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A809" s="1">
         <v>46238</v>
       </c>
@@ -12379,7 +12433,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="810" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A810" s="1">
         <v>46239</v>
       </c>
@@ -12390,7 +12444,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="811" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A811" s="1">
         <v>46240</v>
       </c>
@@ -12401,7 +12455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="812" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A812" s="1">
         <v>46241</v>
       </c>
@@ -12412,7 +12466,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="813" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A813" s="1">
         <v>46242</v>
       </c>
@@ -12423,7 +12477,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="814" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A814" s="1">
         <v>46243</v>
       </c>
@@ -12434,7 +12488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="815" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A815" s="1">
         <v>46244</v>
       </c>
@@ -12445,7 +12499,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="816" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A816" s="1">
         <v>46245</v>
       </c>
@@ -16255,6 +16309,12 @@
       <c r="C1090" t="s">
         <v>19</v>
       </c>
+      <c r="D1090">
+        <v>655.46666500000003</v>
+      </c>
+      <c r="E1090">
+        <v>11</v>
+      </c>
     </row>
     <row r="1091" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1091" s="1">
@@ -16266,6 +16326,12 @@
       <c r="C1091" t="s">
         <v>19</v>
       </c>
+      <c r="D1091">
+        <v>1706.2499989999999</v>
+      </c>
+      <c r="E1091">
+        <v>15</v>
+      </c>
     </row>
     <row r="1092" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1092" s="1">
@@ -16276,6 +16342,12 @@
       </c>
       <c r="C1092" t="s">
         <v>19</v>
+      </c>
+      <c r="D1092">
+        <v>617.23333300000002</v>
+      </c>
+      <c r="E1092">
+        <v>11</v>
       </c>
     </row>
     <row r="1093" spans="1:5" x14ac:dyDescent="0.35">
@@ -40979,6 +41051,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -41201,27 +41293,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41240,25 +41331,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="715" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13CF1752-57E6-4869-905C-10D7172555AA}"/>
+  <xr:revisionPtr revIDLastSave="723" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C084AD88-8CF3-40F8-AE31-0234A71C0420}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -3646,6 +3646,12 @@
       <c r="C181" t="s">
         <v>18</v>
       </c>
+      <c r="D181">
+        <v>1743</v>
+      </c>
+      <c r="E181">
+        <v>33</v>
+      </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
@@ -3657,6 +3663,12 @@
       <c r="C182" t="s">
         <v>18</v>
       </c>
+      <c r="D182">
+        <v>3015</v>
+      </c>
+      <c r="E182">
+        <v>38</v>
+      </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
@@ -8394,6 +8406,12 @@
       <c r="C515" t="s">
         <v>19</v>
       </c>
+      <c r="D515">
+        <v>15827</v>
+      </c>
+      <c r="E515">
+        <v>165</v>
+      </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
@@ -8405,6 +8423,12 @@
       <c r="C516" t="s">
         <v>19</v>
       </c>
+      <c r="D516">
+        <v>16735</v>
+      </c>
+      <c r="E516">
+        <v>181</v>
+      </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
@@ -12377,6 +12401,12 @@
       <c r="C804" t="s">
         <v>18</v>
       </c>
+      <c r="D804">
+        <v>2242.0333340000002</v>
+      </c>
+      <c r="E804">
+        <v>37</v>
+      </c>
     </row>
     <row r="805" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A805" s="1">
@@ -12388,6 +12418,12 @@
       <c r="C805" t="s">
         <v>18</v>
       </c>
+      <c r="D805">
+        <v>3969.7333359999998</v>
+      </c>
+      <c r="E805">
+        <v>55</v>
+      </c>
     </row>
     <row r="806" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A806" s="1">
@@ -16360,6 +16396,12 @@
       <c r="C1093" t="s">
         <v>19</v>
       </c>
+      <c r="D1093">
+        <v>2242.0333340000002</v>
+      </c>
+      <c r="E1093">
+        <v>37</v>
+      </c>
     </row>
     <row r="1094" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1094" s="1">
@@ -16370,6 +16412,12 @@
       </c>
       <c r="C1094" t="s">
         <v>19</v>
+      </c>
+      <c r="D1094">
+        <v>3969.7333359999998</v>
+      </c>
+      <c r="E1094">
+        <v>55</v>
       </c>
     </row>
     <row r="1095" spans="1:5" x14ac:dyDescent="0.35">
@@ -41051,26 +41099,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -41293,26 +41321,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41331,6 +41360,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="723" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C084AD88-8CF3-40F8-AE31-0234A71C0420}"/>
+  <xr:revisionPtr revIDLastSave="731" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DC0C227-ABD1-4609-9753-884D4ACE10C2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -3680,6 +3680,12 @@
       <c r="C183" t="s">
         <v>18</v>
       </c>
+      <c r="D183">
+        <v>2583</v>
+      </c>
+      <c r="E183">
+        <v>42</v>
+      </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
@@ -3691,6 +3697,12 @@
       <c r="C184" t="s">
         <v>18</v>
       </c>
+      <c r="D184">
+        <v>4490</v>
+      </c>
+      <c r="E184">
+        <v>49</v>
+      </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
@@ -3702,6 +3714,12 @@
       <c r="C185" t="s">
         <v>18</v>
       </c>
+      <c r="D185">
+        <v>3918</v>
+      </c>
+      <c r="E185">
+        <v>52</v>
+      </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
@@ -8440,6 +8458,12 @@
       <c r="C517" t="s">
         <v>19</v>
       </c>
+      <c r="D517">
+        <v>18385</v>
+      </c>
+      <c r="E517">
+        <v>226</v>
+      </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
@@ -8451,6 +8475,12 @@
       <c r="C518" t="s">
         <v>19</v>
       </c>
+      <c r="D518">
+        <v>13307</v>
+      </c>
+      <c r="E518">
+        <v>152</v>
+      </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
@@ -8462,6 +8492,12 @@
       <c r="C519" t="s">
         <v>19</v>
       </c>
+      <c r="D519">
+        <v>12026</v>
+      </c>
+      <c r="E519">
+        <v>138</v>
+      </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
@@ -12435,6 +12471,12 @@
       <c r="C806" t="s">
         <v>18</v>
       </c>
+      <c r="D806">
+        <v>453.33333399999998</v>
+      </c>
+      <c r="E806">
+        <v>6</v>
+      </c>
     </row>
     <row r="807" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A807" s="1">
@@ -12446,6 +12488,12 @@
       <c r="C807" t="s">
         <v>18</v>
       </c>
+      <c r="D807">
+        <v>0</v>
+      </c>
+      <c r="E807">
+        <v>0</v>
+      </c>
     </row>
     <row r="808" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A808" s="1">
@@ -12457,6 +12505,12 @@
       <c r="C808" t="s">
         <v>18</v>
       </c>
+      <c r="D808">
+        <v>290.83333499999998</v>
+      </c>
+      <c r="E808">
+        <v>11</v>
+      </c>
     </row>
     <row r="809" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A809" s="1">
@@ -16430,6 +16484,12 @@
       <c r="C1095" t="s">
         <v>19</v>
       </c>
+      <c r="D1095">
+        <v>4445.1499970000004</v>
+      </c>
+      <c r="E1095">
+        <v>55</v>
+      </c>
     </row>
     <row r="1096" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1096" s="1">
@@ -16441,6 +16501,12 @@
       <c r="C1096" t="s">
         <v>19</v>
       </c>
+      <c r="D1096">
+        <v>0</v>
+      </c>
+      <c r="E1096">
+        <v>0</v>
+      </c>
     </row>
     <row r="1097" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1097" s="1">
@@ -16451,6 +16517,12 @@
       </c>
       <c r="C1097" t="s">
         <v>19</v>
+      </c>
+      <c r="D1097">
+        <v>1255.7500050000001</v>
+      </c>
+      <c r="E1097">
+        <v>27</v>
       </c>
     </row>
     <row r="1098" spans="1:5" x14ac:dyDescent="0.35">
@@ -41322,6 +41394,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
@@ -41330,15 +41411,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -41361,6 +41433,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -41371,14 +41451,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="731" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DC0C227-ABD1-4609-9753-884D4ACE10C2}"/>
+  <xr:revisionPtr revIDLastSave="739" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC38C800-DBFA-44AE-932C-A94DD662FDEE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -3731,6 +3731,12 @@
       <c r="C186" t="s">
         <v>18</v>
       </c>
+      <c r="D186">
+        <v>4460</v>
+      </c>
+      <c r="E186">
+        <v>80</v>
+      </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
@@ -8509,6 +8515,12 @@
       <c r="C520" t="s">
         <v>19</v>
       </c>
+      <c r="D520">
+        <v>13142</v>
+      </c>
+      <c r="E520">
+        <v>147</v>
+      </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
@@ -12522,6 +12534,12 @@
       <c r="C809" t="s">
         <v>18</v>
       </c>
+      <c r="D809">
+        <v>128.33333300000001</v>
+      </c>
+      <c r="E809">
+        <v>2</v>
+      </c>
     </row>
     <row r="810" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A810" s="1">
@@ -16534,6 +16552,12 @@
       </c>
       <c r="C1098" t="s">
         <v>19</v>
+      </c>
+      <c r="D1098">
+        <v>2311.2750000000001</v>
+      </c>
+      <c r="E1098">
+        <v>17</v>
       </c>
     </row>
     <row r="1099" spans="1:5" x14ac:dyDescent="0.35">
@@ -41171,6 +41195,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -41393,27 +41437,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41432,25 +41475,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="739" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC38C800-DBFA-44AE-932C-A94DD662FDEE}"/>
+  <xr:revisionPtr revIDLastSave="747" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9F940E9-AE16-4F76-922F-640320E257CB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -3748,6 +3748,12 @@
       <c r="C187" t="s">
         <v>18</v>
       </c>
+      <c r="D187">
+        <v>1519</v>
+      </c>
+      <c r="E187">
+        <v>18</v>
+      </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
@@ -3759,6 +3765,12 @@
       <c r="C188" t="s">
         <v>18</v>
       </c>
+      <c r="D188">
+        <v>4843</v>
+      </c>
+      <c r="E188">
+        <v>43</v>
+      </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
@@ -3770,6 +3782,12 @@
       <c r="C189" t="s">
         <v>18</v>
       </c>
+      <c r="D189">
+        <v>2086</v>
+      </c>
+      <c r="E189">
+        <v>32</v>
+      </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
@@ -3781,6 +3799,12 @@
       <c r="C190" t="s">
         <v>18</v>
       </c>
+      <c r="D190">
+        <v>4276</v>
+      </c>
+      <c r="E190">
+        <v>48</v>
+      </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
@@ -3792,6 +3816,12 @@
       <c r="C191" t="s">
         <v>18</v>
       </c>
+      <c r="D191">
+        <v>2868</v>
+      </c>
+      <c r="E191">
+        <v>36</v>
+      </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
@@ -3803,8 +3833,14 @@
       <c r="C192" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D192">
+        <v>5488</v>
+      </c>
+      <c r="E192">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>46245</v>
       </c>
@@ -3814,8 +3850,14 @@
       <c r="C193" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D193">
+        <v>2939</v>
+      </c>
+      <c r="E193">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>46246</v>
       </c>
@@ -3825,8 +3867,14 @@
       <c r="C194" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D194">
+        <v>3083</v>
+      </c>
+      <c r="E194">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>46247</v>
       </c>
@@ -3836,8 +3884,14 @@
       <c r="C195" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D195">
+        <v>3599</v>
+      </c>
+      <c r="E195">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>46248</v>
       </c>
@@ -3847,8 +3901,14 @@
       <c r="C196" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D196">
+        <v>6062</v>
+      </c>
+      <c r="E196">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>46249</v>
       </c>
@@ -3858,8 +3918,14 @@
       <c r="C197" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D197">
+        <v>3861</v>
+      </c>
+      <c r="E197">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>46250</v>
       </c>
@@ -3869,8 +3935,14 @@
       <c r="C198" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D198">
+        <v>2353</v>
+      </c>
+      <c r="E198">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>46251</v>
       </c>
@@ -3880,8 +3952,14 @@
       <c r="C199" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D199">
+        <v>3312</v>
+      </c>
+      <c r="E199">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>46252</v>
       </c>
@@ -3892,7 +3970,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>46253</v>
       </c>
@@ -3903,7 +3981,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>46254</v>
       </c>
@@ -3914,7 +3992,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>46255</v>
       </c>
@@ -3925,7 +4003,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>46256</v>
       </c>
@@ -3936,7 +4014,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>46257</v>
       </c>
@@ -3947,7 +4025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>46258</v>
       </c>
@@ -3958,7 +4036,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>46259</v>
       </c>
@@ -3969,7 +4047,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>46260</v>
       </c>
@@ -8532,6 +8610,12 @@
       <c r="C521" t="s">
         <v>19</v>
       </c>
+      <c r="D521">
+        <v>14291</v>
+      </c>
+      <c r="E521">
+        <v>143</v>
+      </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
@@ -8543,6 +8627,12 @@
       <c r="C522" t="s">
         <v>19</v>
       </c>
+      <c r="D522">
+        <v>17469</v>
+      </c>
+      <c r="E522">
+        <v>216</v>
+      </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
@@ -8554,6 +8644,12 @@
       <c r="C523" t="s">
         <v>19</v>
       </c>
+      <c r="D523">
+        <v>20130</v>
+      </c>
+      <c r="E523">
+        <v>297</v>
+      </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
@@ -8565,6 +8661,12 @@
       <c r="C524" t="s">
         <v>19</v>
       </c>
+      <c r="D524">
+        <v>16716</v>
+      </c>
+      <c r="E524">
+        <v>192</v>
+      </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
@@ -8576,6 +8678,12 @@
       <c r="C525" t="s">
         <v>19</v>
       </c>
+      <c r="D525">
+        <v>12738</v>
+      </c>
+      <c r="E525">
+        <v>130</v>
+      </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A526" s="1">
@@ -8587,6 +8695,12 @@
       <c r="C526" t="s">
         <v>19</v>
       </c>
+      <c r="D526">
+        <v>14619</v>
+      </c>
+      <c r="E526">
+        <v>173</v>
+      </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
@@ -8598,6 +8712,12 @@
       <c r="C527" t="s">
         <v>19</v>
       </c>
+      <c r="D527">
+        <v>15308</v>
+      </c>
+      <c r="E527">
+        <v>158</v>
+      </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
@@ -8609,8 +8729,14 @@
       <c r="C528" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D528">
+        <v>9813</v>
+      </c>
+      <c r="E528">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A529" s="1">
         <v>46247</v>
       </c>
@@ -8620,8 +8746,14 @@
       <c r="C529" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D529">
+        <v>14712</v>
+      </c>
+      <c r="E529">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A530" s="1">
         <v>46248</v>
       </c>
@@ -8631,8 +8763,14 @@
       <c r="C530" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D530">
+        <v>19430</v>
+      </c>
+      <c r="E530">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A531" s="1">
         <v>46249</v>
       </c>
@@ -8642,8 +8780,14 @@
       <c r="C531" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D531">
+        <v>14844</v>
+      </c>
+      <c r="E531">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A532" s="1">
         <v>46250</v>
       </c>
@@ -8653,8 +8797,14 @@
       <c r="C532" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D532">
+        <v>13997</v>
+      </c>
+      <c r="E532">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A533" s="1">
         <v>46251</v>
       </c>
@@ -8664,8 +8814,14 @@
       <c r="C533" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D533">
+        <v>13937</v>
+      </c>
+      <c r="E533">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A534" s="1">
         <v>46252</v>
       </c>
@@ -8676,7 +8832,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
         <v>46253</v>
       </c>
@@ -8687,7 +8843,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
         <v>46254</v>
       </c>
@@ -8698,7 +8854,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
         <v>46255</v>
       </c>
@@ -8709,7 +8865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A538" s="1">
         <v>46256</v>
       </c>
@@ -8720,7 +8876,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
         <v>46257</v>
       </c>
@@ -8731,7 +8887,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
         <v>46258</v>
       </c>
@@ -8742,7 +8898,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
         <v>46259</v>
       </c>
@@ -8753,7 +8909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
         <v>46260</v>
       </c>
@@ -8764,7 +8920,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
         <v>46261</v>
       </c>
@@ -8775,7 +8931,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A544" s="1">
         <v>46262</v>
       </c>
@@ -12551,6 +12707,12 @@
       <c r="C810" t="s">
         <v>18</v>
       </c>
+      <c r="D810">
+        <v>154.16666900000001</v>
+      </c>
+      <c r="E810">
+        <v>3</v>
+      </c>
     </row>
     <row r="811" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A811" s="1">
@@ -12562,6 +12724,12 @@
       <c r="C811" t="s">
         <v>18</v>
       </c>
+      <c r="D811">
+        <v>347.08333299999998</v>
+      </c>
+      <c r="E811">
+        <v>23</v>
+      </c>
     </row>
     <row r="812" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A812" s="1">
@@ -12573,6 +12741,12 @@
       <c r="C812" t="s">
         <v>18</v>
       </c>
+      <c r="D812">
+        <v>168.33333300000001</v>
+      </c>
+      <c r="E812">
+        <v>4</v>
+      </c>
     </row>
     <row r="813" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A813" s="1">
@@ -12584,6 +12758,12 @@
       <c r="C813" t="s">
         <v>18</v>
       </c>
+      <c r="D813">
+        <v>215.41666799999999</v>
+      </c>
+      <c r="E813">
+        <v>4</v>
+      </c>
     </row>
     <row r="814" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A814" s="1">
@@ -12595,6 +12775,12 @@
       <c r="C814" t="s">
         <v>18</v>
       </c>
+      <c r="D814">
+        <v>0</v>
+      </c>
+      <c r="E814">
+        <v>0</v>
+      </c>
     </row>
     <row r="815" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A815" s="1">
@@ -12606,6 +12792,12 @@
       <c r="C815" t="s">
         <v>18</v>
       </c>
+      <c r="D815">
+        <v>58.333333000000003</v>
+      </c>
+      <c r="E815">
+        <v>0</v>
+      </c>
     </row>
     <row r="816" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A816" s="1">
@@ -12617,8 +12809,14 @@
       <c r="C816" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="817" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D816">
+        <v>290.00000299999999</v>
+      </c>
+      <c r="E816">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="817" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A817" s="1">
         <v>46246</v>
       </c>
@@ -12628,8 +12826,14 @@
       <c r="C817" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="818" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D817">
+        <v>305.83333299999998</v>
+      </c>
+      <c r="E817">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="818" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A818" s="1">
         <v>46247</v>
       </c>
@@ -12639,8 +12843,14 @@
       <c r="C818" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="819" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D818">
+        <v>420.00000299999999</v>
+      </c>
+      <c r="E818">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="819" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A819" s="1">
         <v>46248</v>
       </c>
@@ -12650,8 +12860,14 @@
       <c r="C819" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="820" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D819">
+        <v>107.5</v>
+      </c>
+      <c r="E819">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="820" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A820" s="1">
         <v>46249</v>
       </c>
@@ -12661,8 +12877,14 @@
       <c r="C820" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="821" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D820">
+        <v>221.25</v>
+      </c>
+      <c r="E820">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="821" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A821" s="1">
         <v>46250</v>
       </c>
@@ -12672,8 +12894,14 @@
       <c r="C821" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="822" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D821">
+        <v>0</v>
+      </c>
+      <c r="E821">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A822" s="1">
         <v>46251</v>
       </c>
@@ -12683,8 +12911,14 @@
       <c r="C822" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="823" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D822">
+        <v>414.16667100000001</v>
+      </c>
+      <c r="E822">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="823" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A823" s="1">
         <v>46252</v>
       </c>
@@ -12695,7 +12929,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="824" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A824" s="1">
         <v>46253</v>
       </c>
@@ -12706,7 +12940,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="825" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A825" s="1">
         <v>46254</v>
       </c>
@@ -12717,7 +12951,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="826" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A826" s="1">
         <v>46255</v>
       </c>
@@ -12728,7 +12962,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="827" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A827" s="1">
         <v>46256</v>
       </c>
@@ -12739,7 +12973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="828" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A828" s="1">
         <v>46257</v>
       </c>
@@ -12750,7 +12984,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="829" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A829" s="1">
         <v>46258</v>
       </c>
@@ -12761,7 +12995,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="830" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A830" s="1">
         <v>46259</v>
       </c>
@@ -12772,7 +13006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="831" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A831" s="1">
         <v>46260</v>
       </c>
@@ -12783,7 +13017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="832" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A832" s="1">
         <v>46261</v>
       </c>
@@ -16570,6 +16804,12 @@
       <c r="C1099" t="s">
         <v>19</v>
       </c>
+      <c r="D1099">
+        <v>1730.608338</v>
+      </c>
+      <c r="E1099">
+        <v>28</v>
+      </c>
     </row>
     <row r="1100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1100" s="1">
@@ -16581,6 +16821,12 @@
       <c r="C1100" t="s">
         <v>19</v>
       </c>
+      <c r="D1100">
+        <v>2570.9333339999998</v>
+      </c>
+      <c r="E1100">
+        <v>30</v>
+      </c>
     </row>
     <row r="1101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1101" s="1">
@@ -16592,6 +16838,12 @@
       <c r="C1101" t="s">
         <v>19</v>
       </c>
+      <c r="D1101">
+        <v>2694.666655</v>
+      </c>
+      <c r="E1101">
+        <v>37</v>
+      </c>
     </row>
     <row r="1102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1102" s="1">
@@ -16603,6 +16855,12 @@
       <c r="C1102" t="s">
         <v>19</v>
       </c>
+      <c r="D1102">
+        <v>3022.5166610000001</v>
+      </c>
+      <c r="E1102">
+        <v>49</v>
+      </c>
     </row>
     <row r="1103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1103" s="1">
@@ -16614,6 +16872,12 @@
       <c r="C1103" t="s">
         <v>19</v>
       </c>
+      <c r="D1103">
+        <v>0</v>
+      </c>
+      <c r="E1103">
+        <v>0</v>
+      </c>
     </row>
     <row r="1104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1104" s="1">
@@ -16625,8 +16889,14 @@
       <c r="C1104" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1104">
+        <v>1060.2583340000001</v>
+      </c>
+      <c r="E1104">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1105" s="1">
         <v>46245</v>
       </c>
@@ -16636,8 +16906,14 @@
       <c r="C1105" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1105">
+        <v>1739.9999989999999</v>
+      </c>
+      <c r="E1105">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1106" s="1">
         <v>46246</v>
       </c>
@@ -16647,8 +16923,14 @@
       <c r="C1106" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1106">
+        <v>829.99999400000002</v>
+      </c>
+      <c r="E1106">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1107" s="1">
         <v>46247</v>
       </c>
@@ -16658,8 +16940,14 @@
       <c r="C1107" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1107">
+        <v>3309.5833360000001</v>
+      </c>
+      <c r="E1107">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1108" s="1">
         <v>46248</v>
       </c>
@@ -16669,8 +16957,14 @@
       <c r="C1108" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1108">
+        <v>2142.2499870000001</v>
+      </c>
+      <c r="E1108">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1109" s="1">
         <v>46249</v>
       </c>
@@ -16680,8 +16974,14 @@
       <c r="C1109" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1109">
+        <v>2543.7499969999999</v>
+      </c>
+      <c r="E1109">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1110" s="1">
         <v>46250</v>
       </c>
@@ -16691,8 +16991,14 @@
       <c r="C1110" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1110">
+        <v>0</v>
+      </c>
+      <c r="E1110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1111" s="1">
         <v>46251</v>
       </c>
@@ -16702,8 +17008,14 @@
       <c r="C1111" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1111">
+        <v>823.33333100000004</v>
+      </c>
+      <c r="E1111">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1112" s="1">
         <v>46252</v>
       </c>
@@ -16714,7 +17026,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1113" s="1">
         <v>46253</v>
       </c>
@@ -16725,7 +17037,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1114" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1114" s="1">
         <v>46254</v>
       </c>
@@ -16736,7 +17048,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1115" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1115" s="1">
         <v>46255</v>
       </c>
@@ -16747,7 +17059,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1116" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1116" s="1">
         <v>46256</v>
       </c>
@@ -16758,7 +17070,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1117" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1117" s="1">
         <v>46257</v>
       </c>
@@ -16769,7 +17081,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1118" s="1">
         <v>46258</v>
       </c>
@@ -16780,7 +17092,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1119" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1119" s="1">
         <v>46259</v>
       </c>
@@ -16791,7 +17103,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1120" s="1">
         <v>46260</v>
       </c>
@@ -41195,26 +41507,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -41437,26 +41729,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41475,6 +41768,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="747" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9F940E9-AE16-4F76-922F-640320E257CB}"/>
+  <xr:revisionPtr revIDLastSave="755" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{720BD48D-1770-4908-B61C-62EDD19161F6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -3969,6 +3969,12 @@
       <c r="C200" t="s">
         <v>18</v>
       </c>
+      <c r="D200">
+        <v>3514</v>
+      </c>
+      <c r="E200">
+        <v>43</v>
+      </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
@@ -8831,6 +8837,12 @@
       <c r="C534" t="s">
         <v>19</v>
       </c>
+      <c r="D534">
+        <v>16965</v>
+      </c>
+      <c r="E534">
+        <v>166</v>
+      </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
@@ -12928,6 +12940,12 @@
       <c r="C823" t="s">
         <v>18</v>
       </c>
+      <c r="D823">
+        <v>207.91666699999999</v>
+      </c>
+      <c r="E823">
+        <v>9</v>
+      </c>
     </row>
     <row r="824" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A824" s="1">
@@ -17024,6 +17042,12 @@
       </c>
       <c r="C1112" t="s">
         <v>19</v>
+      </c>
+      <c r="D1112">
+        <v>688.50833599999999</v>
+      </c>
+      <c r="E1112">
+        <v>16</v>
       </c>
     </row>
     <row r="1113" spans="1:5" x14ac:dyDescent="0.35">
@@ -41507,6 +41531,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -41729,27 +41773,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41768,25 +41811,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="755" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{720BD48D-1770-4908-B61C-62EDD19161F6}"/>
+  <xr:revisionPtr revIDLastSave="763" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66A9E951-5EFF-4628-A385-8F5C3CCD628A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -3986,6 +3986,12 @@
       <c r="C201" t="s">
         <v>18</v>
       </c>
+      <c r="D201">
+        <v>1803</v>
+      </c>
+      <c r="E201">
+        <v>24</v>
+      </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
@@ -8854,6 +8860,12 @@
       <c r="C535" t="s">
         <v>19</v>
       </c>
+      <c r="D535">
+        <v>13716</v>
+      </c>
+      <c r="E535">
+        <v>145</v>
+      </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
@@ -12957,6 +12969,12 @@
       <c r="C824" t="s">
         <v>18</v>
       </c>
+      <c r="D824">
+        <v>2013.333331</v>
+      </c>
+      <c r="E824">
+        <v>29</v>
+      </c>
     </row>
     <row r="825" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A825" s="1">
@@ -17059,6 +17077,12 @@
       </c>
       <c r="C1113" t="s">
         <v>19</v>
+      </c>
+      <c r="D1113">
+        <v>3764.5450070000002</v>
+      </c>
+      <c r="E1113">
+        <v>35</v>
       </c>
     </row>
     <row r="1114" spans="1:5" x14ac:dyDescent="0.35">
@@ -41542,15 +41566,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -41773,6 +41788,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
   <ds:schemaRefs>
@@ -41785,14 +41809,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41811,6 +41827,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="763" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66A9E951-5EFF-4628-A385-8F5C3CCD628A}"/>
+  <xr:revisionPtr revIDLastSave="771" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC0DBD55-2E83-4CCF-84B6-4AFC8D1852B0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4003,6 +4003,12 @@
       <c r="C202" t="s">
         <v>18</v>
       </c>
+      <c r="D202">
+        <v>2250</v>
+      </c>
+      <c r="E202">
+        <v>29</v>
+      </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
@@ -8877,6 +8883,12 @@
       <c r="C536" t="s">
         <v>19</v>
       </c>
+      <c r="D536">
+        <v>15486</v>
+      </c>
+      <c r="E536">
+        <v>176</v>
+      </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
@@ -12986,6 +12998,12 @@
       <c r="C825" t="s">
         <v>18</v>
       </c>
+      <c r="D825">
+        <v>1074.5333370000001</v>
+      </c>
+      <c r="E825">
+        <v>25</v>
+      </c>
     </row>
     <row r="826" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A826" s="1">
@@ -17094,6 +17112,12 @@
       </c>
       <c r="C1114" t="s">
         <v>19</v>
+      </c>
+      <c r="D1114">
+        <v>4061.666671</v>
+      </c>
+      <c r="E1114">
+        <v>42</v>
       </c>
     </row>
     <row r="1115" spans="1:5" x14ac:dyDescent="0.35">
@@ -41566,6 +41590,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -41788,15 +41821,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
   <ds:schemaRefs>
@@ -41809,6 +41833,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41827,14 +41859,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="771" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC0DBD55-2E83-4CCF-84B6-4AFC8D1852B0}"/>
+  <xr:revisionPtr revIDLastSave="779" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAEB68FB-EFBE-44C3-A435-1138237949A1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue_Daily" sheetId="1" r:id="rId1"/>
@@ -4020,6 +4020,12 @@
       <c r="C203" t="s">
         <v>18</v>
       </c>
+      <c r="D203">
+        <v>3135</v>
+      </c>
+      <c r="E203">
+        <v>45</v>
+      </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
@@ -4031,6 +4037,12 @@
       <c r="C204" t="s">
         <v>18</v>
       </c>
+      <c r="D204">
+        <v>1422</v>
+      </c>
+      <c r="E204">
+        <v>20</v>
+      </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
@@ -4042,6 +4054,12 @@
       <c r="C205" t="s">
         <v>18</v>
       </c>
+      <c r="D205">
+        <v>2033</v>
+      </c>
+      <c r="E205">
+        <v>33</v>
+      </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
@@ -8900,6 +8918,12 @@
       <c r="C537" t="s">
         <v>19</v>
       </c>
+      <c r="D537">
+        <v>13271</v>
+      </c>
+      <c r="E537">
+        <v>155</v>
+      </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A538" s="1">
@@ -8911,6 +8935,12 @@
       <c r="C538" t="s">
         <v>19</v>
       </c>
+      <c r="D538">
+        <v>13877</v>
+      </c>
+      <c r="E538">
+        <v>154</v>
+      </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
@@ -8922,6 +8952,12 @@
       <c r="C539" t="s">
         <v>19</v>
       </c>
+      <c r="D539">
+        <v>8740</v>
+      </c>
+      <c r="E539">
+        <v>98</v>
+      </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
@@ -13015,6 +13051,12 @@
       <c r="C826" t="s">
         <v>18</v>
       </c>
+      <c r="D826">
+        <v>305.83333499999998</v>
+      </c>
+      <c r="E826">
+        <v>8</v>
+      </c>
     </row>
     <row r="827" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A827" s="1">
@@ -13026,6 +13068,12 @@
       <c r="C827" t="s">
         <v>18</v>
       </c>
+      <c r="D827">
+        <v>734.16666499999997</v>
+      </c>
+      <c r="E827">
+        <v>8</v>
+      </c>
     </row>
     <row r="828" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A828" s="1">
@@ -13037,6 +13085,12 @@
       <c r="C828" t="s">
         <v>18</v>
       </c>
+      <c r="D828">
+        <v>0</v>
+      </c>
+      <c r="E828">
+        <v>0</v>
+      </c>
     </row>
     <row r="829" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A829" s="1">
@@ -17130,6 +17184,12 @@
       <c r="C1115" t="s">
         <v>19</v>
       </c>
+      <c r="D1115">
+        <v>3069.1166699999999</v>
+      </c>
+      <c r="E1115">
+        <v>52</v>
+      </c>
     </row>
     <row r="1116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1116" s="1">
@@ -17141,6 +17201,12 @@
       <c r="C1116" t="s">
         <v>19</v>
       </c>
+      <c r="D1116">
+        <v>3221.1083269999999</v>
+      </c>
+      <c r="E1116">
+        <v>55</v>
+      </c>
     </row>
     <row r="1117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1117" s="1">
@@ -17151,6 +17217,12 @@
       </c>
       <c r="C1117" t="s">
         <v>19</v>
+      </c>
+      <c r="D1117">
+        <v>0</v>
+      </c>
+      <c r="E1117">
+        <v>0</v>
       </c>
     </row>
     <row r="1118" spans="1:5" x14ac:dyDescent="0.35">
@@ -41579,26 +41651,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -41821,26 +41873,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41859,6 +41912,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="779" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAEB68FB-EFBE-44C3-A435-1138237949A1}"/>
+  <xr:revisionPtr revIDLastSave="789" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25AF4072-7D4E-4F78-841C-955C2CF39923}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue_Daily" sheetId="1" r:id="rId1"/>
@@ -4071,6 +4071,12 @@
       <c r="C206" t="s">
         <v>18</v>
       </c>
+      <c r="D206">
+        <v>2227</v>
+      </c>
+      <c r="E206">
+        <v>32</v>
+      </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
@@ -8969,6 +8975,12 @@
       <c r="C540" t="s">
         <v>19</v>
       </c>
+      <c r="D540">
+        <v>11604</v>
+      </c>
+      <c r="E540">
+        <v>127</v>
+      </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
@@ -13072,7 +13084,7 @@
         <v>734.16666499999997</v>
       </c>
       <c r="E827">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="828" spans="1:5" x14ac:dyDescent="0.35">
@@ -13102,6 +13114,12 @@
       <c r="C829" t="s">
         <v>18</v>
       </c>
+      <c r="D829">
+        <v>420.41666600000002</v>
+      </c>
+      <c r="E829">
+        <v>13</v>
+      </c>
     </row>
     <row r="830" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A830" s="1">
@@ -17205,7 +17223,7 @@
         <v>3221.1083269999999</v>
       </c>
       <c r="E1116">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1117" spans="1:5" x14ac:dyDescent="0.35">
@@ -17234,6 +17252,12 @@
       </c>
       <c r="C1118" t="s">
         <v>19</v>
+      </c>
+      <c r="D1118">
+        <v>3442.2916519999999</v>
+      </c>
+      <c r="E1118">
+        <v>51</v>
       </c>
     </row>
     <row r="1119" spans="1:5" x14ac:dyDescent="0.35">
@@ -41651,6 +41675,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -41873,27 +41917,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41912,25 +41955,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="789" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25AF4072-7D4E-4F78-841C-955C2CF39923}"/>
+  <xr:revisionPtr revIDLastSave="798" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DE940E5-4DA3-4A99-8A64-CB9DDF670273}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue_Daily" sheetId="1" r:id="rId1"/>
@@ -4088,6 +4088,12 @@
       <c r="C207" t="s">
         <v>18</v>
       </c>
+      <c r="D207">
+        <v>4282</v>
+      </c>
+      <c r="E207">
+        <v>54</v>
+      </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
@@ -4099,8 +4105,14 @@
       <c r="C208" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D208">
+        <v>3388</v>
+      </c>
+      <c r="E208">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>46261</v>
       </c>
@@ -4110,8 +4122,14 @@
       <c r="C209" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D209">
+        <v>3746</v>
+      </c>
+      <c r="E209">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>46262</v>
       </c>
@@ -4122,7 +4140,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>46263</v>
       </c>
@@ -4133,7 +4151,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>46264</v>
       </c>
@@ -4144,7 +4162,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>46265</v>
       </c>
@@ -4155,7 +4173,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>46266</v>
       </c>
@@ -4166,7 +4184,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>46267</v>
       </c>
@@ -4177,7 +4195,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>46268</v>
       </c>
@@ -4188,7 +4206,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>46269</v>
       </c>
@@ -4199,7 +4217,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>46270</v>
       </c>
@@ -4210,7 +4228,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>46271</v>
       </c>
@@ -4221,7 +4239,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>46272</v>
       </c>
@@ -4232,7 +4250,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>46273</v>
       </c>
@@ -4243,7 +4261,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>46274</v>
       </c>
@@ -4254,7 +4272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>46275</v>
       </c>
@@ -4265,7 +4283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>46276</v>
       </c>
@@ -8992,6 +9010,12 @@
       <c r="C541" t="s">
         <v>19</v>
       </c>
+      <c r="D541">
+        <v>16171</v>
+      </c>
+      <c r="E541">
+        <v>149</v>
+      </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
@@ -9003,6 +9027,12 @@
       <c r="C542" t="s">
         <v>19</v>
       </c>
+      <c r="D542">
+        <v>14754</v>
+      </c>
+      <c r="E542">
+        <v>171</v>
+      </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
@@ -9014,6 +9044,12 @@
       <c r="C543" t="s">
         <v>19</v>
       </c>
+      <c r="D543">
+        <v>12171</v>
+      </c>
+      <c r="E543">
+        <v>133</v>
+      </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A544" s="1">
@@ -13131,6 +13167,12 @@
       <c r="C830" t="s">
         <v>18</v>
       </c>
+      <c r="D830">
+        <v>385</v>
+      </c>
+      <c r="E830">
+        <v>11</v>
+      </c>
     </row>
     <row r="831" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A831" s="1">
@@ -13142,6 +13184,12 @@
       <c r="C831" t="s">
         <v>18</v>
       </c>
+      <c r="D831">
+        <v>434.58333599999997</v>
+      </c>
+      <c r="E831">
+        <v>13</v>
+      </c>
     </row>
     <row r="832" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A832" s="1">
@@ -13153,6 +13201,12 @@
       <c r="C832" t="s">
         <v>18</v>
       </c>
+      <c r="D832">
+        <v>282.35000200000002</v>
+      </c>
+      <c r="E832">
+        <v>9</v>
+      </c>
     </row>
     <row r="833" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A833" s="1">
@@ -17257,7 +17311,7 @@
         <v>3442.2916519999999</v>
       </c>
       <c r="E1118">
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1119" spans="1:5" x14ac:dyDescent="0.35">
@@ -17270,6 +17324,12 @@
       <c r="C1119" t="s">
         <v>19</v>
       </c>
+      <c r="D1119">
+        <v>3763.4583309999998</v>
+      </c>
+      <c r="E1119">
+        <v>39</v>
+      </c>
     </row>
     <row r="1120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1120" s="1">
@@ -17281,8 +17341,14 @@
       <c r="C1120" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1120">
+        <v>2455.666667</v>
+      </c>
+      <c r="E1120">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1121" s="1">
         <v>46261</v>
       </c>
@@ -17292,8 +17358,14 @@
       <c r="C1121" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="1122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1121">
+        <v>1964.9999989999999</v>
+      </c>
+      <c r="E1121">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1122" s="1">
         <v>46262</v>
       </c>
@@ -17304,7 +17376,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1123" s="1">
         <v>46263</v>
       </c>
@@ -17315,7 +17387,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1124" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1124" s="1">
         <v>46264</v>
       </c>
@@ -17326,7 +17398,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1125" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1125" s="1">
         <v>46265</v>
       </c>
@@ -17337,7 +17409,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1126" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1126" s="1">
         <v>46266</v>
       </c>
@@ -17348,7 +17420,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1127" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1127" s="1">
         <v>46267</v>
       </c>
@@ -17359,7 +17431,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1128" s="1">
         <v>46268</v>
       </c>
@@ -17370,7 +17442,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1129" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1129" s="1">
         <v>46269</v>
       </c>
@@ -17381,7 +17453,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1130" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1130" s="1">
         <v>46270</v>
       </c>
@@ -17392,7 +17464,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1131" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1131" s="1">
         <v>46271</v>
       </c>
@@ -17403,7 +17475,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1132" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1132" s="1">
         <v>46272</v>
       </c>
@@ -17414,7 +17486,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1133" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1133" s="1">
         <v>46273</v>
       </c>
@@ -17425,7 +17497,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1134" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1134" s="1">
         <v>46274</v>
       </c>
@@ -17436,7 +17508,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1135" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1135" s="1">
         <v>46275</v>
       </c>
@@ -17447,7 +17519,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="1136" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1136" s="1">
         <v>46276</v>
       </c>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="798" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DE940E5-4DA3-4A99-8A64-CB9DDF670273}"/>
+  <xr:revisionPtr revIDLastSave="806" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C38FC07A-1719-49F9-A2F4-C4E140891FFC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
   <sheets>
     <sheet name="Revenue_Daily" sheetId="1" r:id="rId1"/>
@@ -4139,6 +4139,12 @@
       <c r="C210" t="s">
         <v>18</v>
       </c>
+      <c r="D210">
+        <v>6411</v>
+      </c>
+      <c r="E210">
+        <v>91</v>
+      </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
@@ -4150,6 +4156,12 @@
       <c r="C211" t="s">
         <v>18</v>
       </c>
+      <c r="D211">
+        <v>2694</v>
+      </c>
+      <c r="E211">
+        <v>32</v>
+      </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
@@ -4161,6 +4173,12 @@
       <c r="C212" t="s">
         <v>18</v>
       </c>
+      <c r="D212">
+        <v>6175</v>
+      </c>
+      <c r="E212">
+        <v>77</v>
+      </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
@@ -9061,8 +9079,14 @@
       <c r="C544" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D544">
+        <v>13386</v>
+      </c>
+      <c r="E544">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A545" s="1">
         <v>46263</v>
       </c>
@@ -9072,8 +9096,14 @@
       <c r="C545" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D545">
+        <v>14796</v>
+      </c>
+      <c r="E545">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A546" s="1">
         <v>46264</v>
       </c>
@@ -9083,8 +9113,14 @@
       <c r="C546" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D546">
+        <v>9647</v>
+      </c>
+      <c r="E546">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A547" s="1">
         <v>46265</v>
       </c>
@@ -9095,7 +9131,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A548" s="1">
         <v>46266</v>
       </c>
@@ -9106,7 +9142,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A549" s="1">
         <v>46267</v>
       </c>
@@ -9117,7 +9153,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A550" s="1">
         <v>46268</v>
       </c>
@@ -9128,7 +9164,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A551" s="1">
         <v>46269</v>
       </c>
@@ -9139,7 +9175,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A552" s="1">
         <v>46270</v>
       </c>
@@ -9150,7 +9186,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A553" s="1">
         <v>46271</v>
       </c>
@@ -9161,7 +9197,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A554" s="1">
         <v>46272</v>
       </c>
@@ -9172,7 +9208,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A555" s="1">
         <v>46273</v>
       </c>
@@ -9183,7 +9219,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A556" s="1">
         <v>46274</v>
       </c>
@@ -9194,7 +9230,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A557" s="1">
         <v>46275</v>
       </c>
@@ -9205,7 +9241,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A558" s="1">
         <v>46276</v>
       </c>
@@ -9216,7 +9252,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A559" s="1">
         <v>46277</v>
       </c>
@@ -9227,7 +9263,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A560" s="1">
         <v>46278</v>
       </c>
@@ -13208,7 +13244,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="833" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A833" s="1">
         <v>46262</v>
       </c>
@@ -13218,8 +13254,14 @@
       <c r="C833" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="834" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D833">
+        <v>220</v>
+      </c>
+      <c r="E833">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="834" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A834" s="1">
         <v>46263</v>
       </c>
@@ -13229,8 +13271,14 @@
       <c r="C834" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="835" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D834">
+        <v>698.33333500000003</v>
+      </c>
+      <c r="E834">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="835" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A835" s="1">
         <v>46264</v>
       </c>
@@ -13240,8 +13288,14 @@
       <c r="C835" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="836" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D835">
+        <v>0</v>
+      </c>
+      <c r="E835">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="836" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A836" s="1">
         <v>46265</v>
       </c>
@@ -13252,7 +13306,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="837" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A837" s="1">
         <v>46266</v>
       </c>
@@ -13263,7 +13317,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="838" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A838" s="1">
         <v>46267</v>
       </c>
@@ -13274,7 +13328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="839" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A839" s="1">
         <v>46268</v>
       </c>
@@ -13285,7 +13339,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="840" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A840" s="1">
         <v>46269</v>
       </c>
@@ -13296,7 +13350,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="841" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A841" s="1">
         <v>46270</v>
       </c>
@@ -13307,7 +13361,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="842" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A842" s="1">
         <v>46271</v>
       </c>
@@ -13318,7 +13372,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="843" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A843" s="1">
         <v>46272</v>
       </c>
@@ -13329,7 +13383,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="844" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A844" s="1">
         <v>46273</v>
       </c>
@@ -13340,7 +13394,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="845" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A845" s="1">
         <v>46274</v>
       </c>
@@ -13351,7 +13405,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="846" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A846" s="1">
         <v>46275</v>
       </c>
@@ -13362,7 +13416,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="847" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A847" s="1">
         <v>46276</v>
       </c>
@@ -13373,7 +13427,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="848" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A848" s="1">
         <v>46277</v>
       </c>
@@ -17375,6 +17429,12 @@
       <c r="C1122" t="s">
         <v>19</v>
       </c>
+      <c r="D1122">
+        <v>695.41666499999997</v>
+      </c>
+      <c r="E1122">
+        <v>12</v>
+      </c>
     </row>
     <row r="1123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1123" s="1">
@@ -17386,6 +17446,12 @@
       <c r="C1123" t="s">
         <v>19</v>
       </c>
+      <c r="D1123">
+        <v>2323.7499969999999</v>
+      </c>
+      <c r="E1123">
+        <v>41</v>
+      </c>
     </row>
     <row r="1124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1124" s="1">
@@ -17396,6 +17462,12 @@
       </c>
       <c r="C1124" t="s">
         <v>19</v>
+      </c>
+      <c r="D1124">
+        <v>0</v>
+      </c>
+      <c r="E1124">
+        <v>0</v>
       </c>
     </row>
     <row r="1125" spans="1:5" x14ac:dyDescent="0.35">
@@ -41747,26 +41819,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -41989,26 +42041,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42027,6 +42080,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="806" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C38FC07A-1719-49F9-A2F4-C4E140891FFC}"/>
+  <xr:revisionPtr revIDLastSave="814" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85FCCA5A-6A65-4A83-8C4A-24D0EB1795A0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4190,6 +4190,12 @@
       <c r="C213" t="s">
         <v>18</v>
       </c>
+      <c r="D213">
+        <v>2206</v>
+      </c>
+      <c r="E213">
+        <v>33</v>
+      </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
@@ -9130,6 +9136,12 @@
       <c r="C547" t="s">
         <v>19</v>
       </c>
+      <c r="D547">
+        <v>11564</v>
+      </c>
+      <c r="E547">
+        <v>89</v>
+      </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A548" s="1">
@@ -13305,6 +13317,12 @@
       <c r="C836" t="s">
         <v>18</v>
       </c>
+      <c r="D836">
+        <v>0</v>
+      </c>
+      <c r="E836">
+        <v>0</v>
+      </c>
     </row>
     <row r="837" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A837" s="1">
@@ -17479,6 +17497,12 @@
       </c>
       <c r="C1125" t="s">
         <v>19</v>
+      </c>
+      <c r="D1125">
+        <v>270.83333399999998</v>
+      </c>
+      <c r="E1125">
+        <v>6</v>
       </c>
     </row>
     <row r="1126" spans="1:5" x14ac:dyDescent="0.35">
@@ -41819,6 +41843,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -42041,27 +42085,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42080,25 +42123,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="814" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85FCCA5A-6A65-4A83-8C4A-24D0EB1795A0}"/>
+  <xr:revisionPtr revIDLastSave="826" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65D86E9D-05FC-4BDB-90E5-07CA0B31E563}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4191,10 +4191,10 @@
         <v>18</v>
       </c>
       <c r="D213">
-        <v>2206</v>
+        <v>2225</v>
       </c>
       <c r="E213">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.35">
@@ -4207,6 +4207,12 @@
       <c r="C214" t="s">
         <v>18</v>
       </c>
+      <c r="D214">
+        <v>2206</v>
+      </c>
+      <c r="E214">
+        <v>33</v>
+      </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
@@ -4218,6 +4224,12 @@
       <c r="C215" t="s">
         <v>18</v>
       </c>
+      <c r="D215">
+        <v>4783</v>
+      </c>
+      <c r="E215">
+        <v>61</v>
+      </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
@@ -9137,10 +9149,10 @@
         <v>19</v>
       </c>
       <c r="D547">
-        <v>11564</v>
+        <v>8792</v>
       </c>
       <c r="E547">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.35">
@@ -9153,6 +9165,12 @@
       <c r="C548" t="s">
         <v>19</v>
       </c>
+      <c r="D548">
+        <v>11564</v>
+      </c>
+      <c r="E548">
+        <v>89</v>
+      </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A549" s="1">
@@ -9164,6 +9182,12 @@
       <c r="C549" t="s">
         <v>19</v>
       </c>
+      <c r="D549">
+        <v>9003</v>
+      </c>
+      <c r="E549">
+        <v>86</v>
+      </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A550" s="1">
@@ -13334,6 +13358,12 @@
       <c r="C837" t="s">
         <v>18</v>
       </c>
+      <c r="D837">
+        <v>531.66666399999997</v>
+      </c>
+      <c r="E837">
+        <v>13</v>
+      </c>
     </row>
     <row r="838" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A838" s="1">
@@ -13345,6 +13375,12 @@
       <c r="C838" t="s">
         <v>18</v>
       </c>
+      <c r="D838">
+        <v>445.24999800000001</v>
+      </c>
+      <c r="E838">
+        <v>3</v>
+      </c>
     </row>
     <row r="839" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A839" s="1">
@@ -17515,6 +17551,12 @@
       <c r="C1126" t="s">
         <v>19</v>
       </c>
+      <c r="D1126">
+        <v>1754.8333339999999</v>
+      </c>
+      <c r="E1126">
+        <v>26</v>
+      </c>
     </row>
     <row r="1127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1127" s="1">
@@ -17525,6 +17567,12 @@
       </c>
       <c r="C1127" t="s">
         <v>19</v>
+      </c>
+      <c r="D1127">
+        <v>4242.9333379999998</v>
+      </c>
+      <c r="E1127">
+        <v>57</v>
       </c>
     </row>
     <row r="1128" spans="1:5" x14ac:dyDescent="0.35">
@@ -41852,17 +41900,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -42085,6 +42122,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
   <ds:schemaRefs>
@@ -42094,17 +42142,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42123,6 +42160,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="826" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65D86E9D-05FC-4BDB-90E5-07CA0B31E563}"/>
+  <xr:revisionPtr revIDLastSave="834" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C5C250C-BFF7-43D0-BE3F-9382E3D391EA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4241,6 +4241,12 @@
       <c r="C216" t="s">
         <v>18</v>
       </c>
+      <c r="D216">
+        <v>1247</v>
+      </c>
+      <c r="E216">
+        <v>29</v>
+      </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
@@ -9199,6 +9205,12 @@
       <c r="C550" t="s">
         <v>19</v>
       </c>
+      <c r="D550">
+        <v>9313</v>
+      </c>
+      <c r="E550">
+        <v>101</v>
+      </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A551" s="1">
@@ -13392,6 +13404,12 @@
       <c r="C839" t="s">
         <v>18</v>
       </c>
+      <c r="D839">
+        <v>3461.5833429999998</v>
+      </c>
+      <c r="E839">
+        <v>84</v>
+      </c>
     </row>
     <row r="840" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A840" s="1">
@@ -17584,6 +17602,12 @@
       </c>
       <c r="C1128" t="s">
         <v>19</v>
+      </c>
+      <c r="D1128">
+        <v>7177.0000120000004</v>
+      </c>
+      <c r="E1128">
+        <v>51</v>
       </c>
     </row>
     <row r="1129" spans="1:5" x14ac:dyDescent="0.35">
@@ -41891,15 +41915,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -42122,6 +42137,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -42134,14 +42158,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42156,6 +42172,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="834" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C5C250C-BFF7-43D0-BE3F-9382E3D391EA}"/>
+  <xr:revisionPtr revIDLastSave="842" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B40DC02A-6F48-4DA5-BA28-DB6C5FC629E5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4258,6 +4258,12 @@
       <c r="C217" t="s">
         <v>18</v>
       </c>
+      <c r="D217">
+        <v>1242</v>
+      </c>
+      <c r="E217">
+        <v>15</v>
+      </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
@@ -4269,6 +4275,12 @@
       <c r="C218" t="s">
         <v>18</v>
       </c>
+      <c r="D218">
+        <v>2420</v>
+      </c>
+      <c r="E218">
+        <v>35</v>
+      </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
@@ -4280,6 +4292,12 @@
       <c r="C219" t="s">
         <v>18</v>
       </c>
+      <c r="D219">
+        <v>7176</v>
+      </c>
+      <c r="E219">
+        <v>65</v>
+      </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
@@ -9222,6 +9240,12 @@
       <c r="C551" t="s">
         <v>19</v>
       </c>
+      <c r="D551">
+        <v>9606</v>
+      </c>
+      <c r="E551">
+        <v>107</v>
+      </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A552" s="1">
@@ -9233,6 +9257,12 @@
       <c r="C552" t="s">
         <v>19</v>
       </c>
+      <c r="D552">
+        <v>11446</v>
+      </c>
+      <c r="E552">
+        <v>120</v>
+      </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A553" s="1">
@@ -9244,6 +9274,12 @@
       <c r="C553" t="s">
         <v>19</v>
       </c>
+      <c r="D553">
+        <v>9716</v>
+      </c>
+      <c r="E553">
+        <v>122</v>
+      </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A554" s="1">
@@ -13421,6 +13457,12 @@
       <c r="C840" t="s">
         <v>18</v>
       </c>
+      <c r="D840">
+        <v>392.50000399999999</v>
+      </c>
+      <c r="E840">
+        <v>13</v>
+      </c>
     </row>
     <row r="841" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A841" s="1">
@@ -13432,6 +13474,12 @@
       <c r="C841" t="s">
         <v>18</v>
       </c>
+      <c r="D841">
+        <v>427.50000299999999</v>
+      </c>
+      <c r="E841">
+        <v>20</v>
+      </c>
     </row>
     <row r="842" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A842" s="1">
@@ -13443,6 +13491,12 @@
       <c r="C842" t="s">
         <v>18</v>
       </c>
+      <c r="D842">
+        <v>0</v>
+      </c>
+      <c r="E842">
+        <v>0</v>
+      </c>
     </row>
     <row r="843" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A843" s="1">
@@ -17620,6 +17674,12 @@
       <c r="C1129" t="s">
         <v>19</v>
       </c>
+      <c r="D1129">
+        <v>2290.000004</v>
+      </c>
+      <c r="E1129">
+        <v>43</v>
+      </c>
     </row>
     <row r="1130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1130" s="1">
@@ -17631,6 +17691,12 @@
       <c r="C1130" t="s">
         <v>19</v>
       </c>
+      <c r="D1130">
+        <v>4218.7249940000002</v>
+      </c>
+      <c r="E1130">
+        <v>56</v>
+      </c>
     </row>
     <row r="1131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1131" s="1">
@@ -17641,6 +17707,12 @@
       </c>
       <c r="C1131" t="s">
         <v>19</v>
+      </c>
+      <c r="D1131">
+        <v>0</v>
+      </c>
+      <c r="E1131">
+        <v>0</v>
       </c>
     </row>
     <row r="1132" spans="1:5" x14ac:dyDescent="0.35">
@@ -41915,6 +41987,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -42137,15 +42218,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -42158,6 +42230,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42172,14 +42252,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="842" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B40DC02A-6F48-4DA5-BA28-DB6C5FC629E5}"/>
+  <xr:revisionPtr revIDLastSave="850" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E15FB1A2-0B82-468A-8F28-17798C3C35F2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4309,6 +4309,12 @@
       <c r="C220" t="s">
         <v>18</v>
       </c>
+      <c r="D220">
+        <v>7004</v>
+      </c>
+      <c r="E220">
+        <v>86</v>
+      </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
@@ -9291,6 +9297,12 @@
       <c r="C554" t="s">
         <v>19</v>
       </c>
+      <c r="D554">
+        <v>13678</v>
+      </c>
+      <c r="E554">
+        <v>112</v>
+      </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A555" s="1">
@@ -13508,6 +13520,12 @@
       <c r="C843" t="s">
         <v>18</v>
       </c>
+      <c r="D843">
+        <v>0</v>
+      </c>
+      <c r="E843">
+        <v>0</v>
+      </c>
     </row>
     <row r="844" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A844" s="1">
@@ -17724,6 +17742,12 @@
       </c>
       <c r="C1132" t="s">
         <v>19</v>
+      </c>
+      <c r="D1132">
+        <v>1640.416661</v>
+      </c>
+      <c r="E1132">
+        <v>30</v>
       </c>
     </row>
     <row r="1133" spans="1:5" x14ac:dyDescent="0.35">
@@ -41987,15 +42011,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -42218,6 +42233,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -42230,14 +42254,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42252,6 +42268,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="850" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E15FB1A2-0B82-468A-8F28-17798C3C35F2}"/>
+  <xr:revisionPtr revIDLastSave="858" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{591BA24A-A950-4A47-9F58-7866327A7169}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4326,6 +4326,12 @@
       <c r="C221" t="s">
         <v>18</v>
       </c>
+      <c r="D221">
+        <v>4684</v>
+      </c>
+      <c r="E221">
+        <v>75</v>
+      </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
@@ -9314,6 +9320,12 @@
       <c r="C555" t="s">
         <v>19</v>
       </c>
+      <c r="D555">
+        <v>9143</v>
+      </c>
+      <c r="E555">
+        <v>100</v>
+      </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A556" s="1">
@@ -13537,6 +13549,12 @@
       <c r="C844" t="s">
         <v>18</v>
       </c>
+      <c r="D844">
+        <v>412.5</v>
+      </c>
+      <c r="E844">
+        <v>14</v>
+      </c>
     </row>
     <row r="845" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A845" s="1">
@@ -17759,6 +17777,12 @@
       </c>
       <c r="C1133" t="s">
         <v>19</v>
+      </c>
+      <c r="D1133">
+        <v>2615.350003</v>
+      </c>
+      <c r="E1133">
+        <v>32</v>
       </c>
     </row>
     <row r="1134" spans="1:5" x14ac:dyDescent="0.35">
@@ -42011,6 +42035,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6E90AD78CD2654D808DE399282FD773" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32dae6b5de1ea194c39c302cae191d14">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f096a02b-94ae-4b4d-ac09-5638e80be9f2" xmlns:ns3="ac830b42-b323-416c-8481-91c550a6d76d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="947fe34ef1b68bd96db045d283e94614" ns2:_="" ns3:_="">
     <xsd:import namespace="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
@@ -42233,27 +42277,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
+    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f096a02b-94ae-4b4d-ac09-5638e80be9f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E066B38-4FF0-4490-9B99-1B554BAEB978}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42272,25 +42315,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
-    <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" enabled="0" method="" siteId="{b22fbdb1-a88a-4fa0-a06d-78efebe8c721}" removed="1"/>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="858" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{591BA24A-A950-4A47-9F58-7866327A7169}"/>
+  <xr:revisionPtr revIDLastSave="866" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1EFF461-6F85-4E20-8F00-AC535421B6F0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4343,6 +4343,12 @@
       <c r="C222" t="s">
         <v>18</v>
       </c>
+      <c r="D222">
+        <v>3100</v>
+      </c>
+      <c r="E222">
+        <v>43</v>
+      </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
@@ -9337,6 +9343,12 @@
       <c r="C556" t="s">
         <v>19</v>
       </c>
+      <c r="D556">
+        <v>10763</v>
+      </c>
+      <c r="E556">
+        <v>108</v>
+      </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A557" s="1">
@@ -13566,6 +13578,12 @@
       <c r="C845" t="s">
         <v>18</v>
       </c>
+      <c r="D845">
+        <v>5331.0250020000003</v>
+      </c>
+      <c r="E845">
+        <v>64</v>
+      </c>
     </row>
     <row r="846" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A846" s="1">
@@ -17794,6 +17812,12 @@
       </c>
       <c r="C1134" t="s">
         <v>19</v>
+      </c>
+      <c r="D1134">
+        <v>6349.7083339999999</v>
+      </c>
+      <c r="E1134">
+        <v>41</v>
       </c>
     </row>
     <row r="1135" spans="1:5" x14ac:dyDescent="0.35">
@@ -42035,6 +42059,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
@@ -42043,15 +42076,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -42278,20 +42302,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
     <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/F_B_Master_Database.xlsx
+++ b/F_B_Master_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://padaeng.sharepoint.com/sites/PDI/Lifestyle/Shared Documents/Financial Performance/Daily Report/F&amp;B Performance Dashboard/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="866" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1EFF461-6F85-4E20-8F00-AC535421B6F0}"/>
+  <xr:revisionPtr revIDLastSave="874" documentId="8_{2A99627D-46B1-43DB-B3A1-B2E68502899D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4595E297-5266-43F0-9691-0DDC21599C9E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C61F3FE8-D426-4ADB-A5AC-01C777785433}"/>
   </bookViews>
@@ -4360,6 +4360,12 @@
       <c r="C223" t="s">
         <v>18</v>
       </c>
+      <c r="D223">
+        <v>3082</v>
+      </c>
+      <c r="E223">
+        <v>39</v>
+      </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
@@ -9360,6 +9366,12 @@
       <c r="C557" t="s">
         <v>19</v>
       </c>
+      <c r="D557">
+        <v>8984</v>
+      </c>
+      <c r="E557">
+        <v>80</v>
+      </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A558" s="1">
@@ -13595,6 +13607,12 @@
       <c r="C846" t="s">
         <v>18</v>
       </c>
+      <c r="D846">
+        <v>2066.2500009999999</v>
+      </c>
+      <c r="E846">
+        <v>37</v>
+      </c>
     </row>
     <row r="847" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A847" s="1">
@@ -17829,6 +17847,12 @@
       </c>
       <c r="C1135" t="s">
         <v>19</v>
+      </c>
+      <c r="D1135">
+        <v>2502.541667</v>
+      </c>
+      <c r="E1135">
+        <v>24</v>
       </c>
     </row>
     <row r="1136" spans="1:5" x14ac:dyDescent="0.35">
@@ -42059,15 +42083,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="ac830b42-b323-416c-8481-91c550a6d76d" xsi:nil="true"/>
@@ -42076,6 +42091,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -42302,20 +42326,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FF2889-47B3-434E-A467-F2956BC927BB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="ac830b42-b323-416c-8481-91c550a6d76d"/>
     <ds:schemaRef ds:uri="f096a02b-94ae-4b4d-ac09-5638e80be9f2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{506083CA-A091-45D0-9DDA-9BDEFCA2AB3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
